--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104615_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104615_W18.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.567399999999999</v>
+        <v>8.8682</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1331</v>
+        <v>3.9282</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4343</v>
+        <v>4.94</v>
       </c>
       <c r="G2" t="n">
-        <v>6.829</v>
+        <v>6.8064</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3853</v>
+        <v>3.378</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4437</v>
+        <v>3.4284</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3439</v>
+        <v>4.2908</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2948</v>
+        <v>1.2681</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0491</v>
+        <v>3.0227</v>
       </c>
       <c r="M2" t="n">
-        <v>2.4851</v>
+        <v>2.5156</v>
       </c>
       <c r="N2" t="n">
-        <v>2.0905</v>
+        <v>2.1099</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0348</v>
+        <v>0.2894</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1693</v>
+        <v>-0.3139</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1346</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1262</v>
+        <v>6.3774</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2581</v>
+        <v>2.5136</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8681</v>
+        <v>3.8638</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0078</v>
+        <v>5.0196</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9335</v>
+        <v>3.9347</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0743</v>
+        <v>1.0849</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5994</v>
+        <v>3.579</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3307</v>
+        <v>2.313</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4083</v>
+        <v>1.4405</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6028</v>
+        <v>1.6217</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5375</v>
+        <v>-0.3039</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9557</v>
+        <v>-0.6785</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4183</v>
+        <v>0.3746</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1972</v>
+        <v>4.6851</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0349</v>
+        <v>2.4617</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1623</v>
+        <v>2.2235</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9063</v>
+        <v>3.9241</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6535</v>
+        <v>2.662</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2529</v>
+        <v>1.2621</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9112</v>
+        <v>2.9008</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9952</v>
+        <v>1.0233</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9737</v>
+        <v>0.99</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0286</v>
+        <v>-0.556</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8347</v>
+        <v>-0.3904</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1939</v>
+        <v>-0.1656</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6645</v>
+        <v>2.9522</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2411</v>
+        <v>-0.3022</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9055</v>
+        <v>3.2544</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6624</v>
+        <v>2.6708</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5237</v>
+        <v>2.5245</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7345</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.385</v>
+        <v>-0.4039</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1195</v>
+        <v>1.1171</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9278</v>
+        <v>1.9577</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9087</v>
+        <v>2.9284</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5219</v>
+        <v>0.8065</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0393</v>
+        <v>0.0136</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4825</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5049</v>
+        <v>1.9465</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8994</v>
+        <v>-0.7106</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4043</v>
+        <v>2.6571</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9466</v>
+        <v>2.9648</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4241</v>
+        <v>2.4295</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5225</v>
+        <v>0.5353</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6956</v>
+        <v>1.6822</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1358</v>
+        <v>1.1236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5598</v>
+        <v>0.5586</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2511</v>
+        <v>1.2826</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2883</v>
+        <v>1.3058</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9881</v>
+        <v>-0.5631</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3266</v>
+        <v>-0.1165</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6615</v>
+        <v>-0.4466</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1764</v>
+        <v>0.9951</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1936</v>
+        <v>-0.5365</v>
       </c>
       <c r="F7" t="n">
-        <v>1.37</v>
+        <v>1.5316</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5414</v>
+        <v>2.5467</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9839</v>
+        <v>2.9922</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4425</v>
+        <v>-0.4455</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8267</v>
+        <v>0.8063</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6798</v>
+        <v>-0.6933</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7147</v>
+        <v>1.7404</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4773</v>
+        <v>1.4926</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6333</v>
+        <v>0.1721</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8861</v>
+        <v>-0.2047</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2528</v>
+        <v>0.3768</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4959</v>
+        <v>-0.3134</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8661</v>
+        <v>-1.9375</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3702</v>
+        <v>1.6241</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9558</v>
+        <v>1.9443</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2597</v>
+        <v>2.2576</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5715</v>
+        <v>0.5343</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9555</v>
+        <v>0.9373</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.384</v>
+        <v>-0.403</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3842</v>
+        <v>1.4101</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3042</v>
+        <v>1.3203</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.359</v>
+        <v>-0.1683</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1693</v>
+        <v>-0.1955</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1896</v>
+        <v>0.0272</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2946</v>
+        <v>-1.4267</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.27</v>
+        <v>-2.9254</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9754</v>
+        <v>1.4986</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.332</v>
+        <v>-0.3303</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0172</v>
+        <v>-1.0249</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6851</v>
+        <v>0.6946</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3276</v>
+        <v>-0.3467</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4023</v>
+        <v>-0.4212</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0044</v>
+        <v>0.0164</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.216</v>
+        <v>-0.3436</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8347</v>
+        <v>-0.4601</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6188</v>
+        <v>0.1165</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6864</v>
+        <v>-1.6802</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7826</v>
+        <v>-1.7217</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0415</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.7861</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2135</v>
+        <v>0.218</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0023</v>
+        <v>-1.0041</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5093</v>
+        <v>-0.5139</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2771</v>
+        <v>0.2758</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2795</v>
+        <v>-0.2722</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0097</v>
+        <v>0.0163</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1391</v>
+        <v>-0.0697</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1488</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7523</v>
+        <v>-3.8931</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3539</v>
+        <v>-4.6432</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6015</v>
+        <v>0.7501</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1966</v>
+        <v>-1.1929</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4934</v>
+        <v>0.4994</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.69</v>
+        <v>-1.6923</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0372</v>
+        <v>-2.0554</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8406</v>
+        <v>0.8625</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8753</v>
+        <v>-1.0173</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0484</v>
+        <v>-0.3115</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8269</v>
+        <v>-0.7058</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.2587</v>
+        <v>-4.6148</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2274</v>
+        <v>-2.762</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0313</v>
+        <v>-1.8529</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.4508</v>
+        <v>-3.4592</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5209</v>
+        <v>0.5199</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.9717</v>
+        <v>-3.9791</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.6245</v>
+        <v>-3.6492</v>
       </c>
       <c r="K12" t="n">
-        <v>0.27</v>
+        <v>0.2618</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.8945</v>
+        <v>-3.911</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1737</v>
+        <v>0.19</v>
       </c>
       <c r="N12" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8494</v>
+        <v>-1.2043</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6956</v>
+        <v>-0.2023</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1538</v>
+        <v>-1.002</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.7487</v>
+        <v>13.8963</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.408000000000001</v>
+        <v>-6.6356</v>
       </c>
       <c r="F13" t="n">
-        <v>20.1565</v>
+        <v>20.5318</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0811</v>
+        <v>20.1082</v>
       </c>
       <c r="H13" t="n">
-        <v>20.3743</v>
+        <v>20.3909</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2931999999999988</v>
+        <v>-0.2826</v>
       </c>
       <c r="J13" t="n">
-        <v>8.184200000000001</v>
+        <v>7.941399999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>8.9848</v>
+        <v>8.839599999999997</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8005000000000009</v>
+        <v>-0.8980000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>11.8968</v>
+        <v>12.1669</v>
       </c>
       <c r="N13" t="n">
-        <v>11.3895</v>
+        <v>11.5512</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5073</v>
+        <v>0.6155999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8784</v>
+        <v>15.9344</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.990399999999999</v>
+        <v>-2.8722</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.0202</v>
+        <v>-2.9295</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03010000000000024</v>
+        <v>0.05720000000000014</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.342099999999999</v>
+        <v>-3.339700000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>4.3066</v>
+        <v>4.2865</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.6486</v>
+        <v>-7.626200000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9855</v>
+        <v>2.324</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4665</v>
+        <v>1.5618</v>
       </c>
       <c r="F14" t="n">
-        <v>0.519</v>
+        <v>0.7623</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5808</v>
+        <v>3.4497</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.671</v>
+        <v>0.8418</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0902</v>
+        <v>2.6079</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0689</v>
+        <v>4.6214</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9218</v>
+        <v>1.1441</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8529</v>
+        <v>3.4773</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5119</v>
+        <v>-1.1717</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7493</v>
+        <v>-0.3023</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2373</v>
+        <v>-0.8694</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4321</v>
+        <v>-0.0362</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1232</v>
+        <v>-0.7833</v>
       </c>
       <c r="U14" t="n">
-        <v>1.309</v>
+        <v>0.7471</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2756</v>
+        <v>1.1704</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0216</v>
+        <v>0.3383</v>
       </c>
       <c r="F15" t="n">
-        <v>0.254</v>
+        <v>0.8321</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4646</v>
+        <v>-0.4474</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8471</v>
+        <v>-0.491</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6175</v>
+        <v>0.0436</v>
       </c>
       <c r="J15" t="n">
-        <v>4.663</v>
+        <v>0.2389</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1633</v>
+        <v>0.1272</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4997</v>
+        <v>0.1117</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1984</v>
+        <v>-0.6863</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3162</v>
+        <v>-0.6182</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8822</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0963</v>
+        <v>0.1822</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3731</v>
+        <v>0.0994</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2767</v>
+        <v>0.0827</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7057</v>
+        <v>0.3779</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0035</v>
+        <v>-0.0944</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7091</v>
+        <v>0.4723</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4544</v>
+        <v>-1.574</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4891</v>
+        <v>-2.6629</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0347</v>
+        <v>1.0888</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2536</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1416</v>
+        <v>-0.9383</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.8411</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.708</v>
+        <v>-1.4769</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6308</v>
+        <v>-1.7246</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0772</v>
+        <v>0.2477</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2671</v>
+        <v>1.8137</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2571</v>
+        <v>0.5961</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.01</v>
+        <v>1.2176</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>A. LIMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4396</v>
+        <v>0.2457</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9498</v>
+        <v>0.1147</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3893</v>
+        <v>0.1309</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1212</v>
+        <v>-0.0261</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9164</v>
+        <v>-0.3419</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2048</v>
+        <v>0.3159</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7754</v>
+        <v>0.0172</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6478</v>
+        <v>0.0172</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1276</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3458</v>
+        <v>-0.0433</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2685</v>
+        <v>-0.3592</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0772</v>
+        <v>0.3159</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.973</v>
+        <v>0.2717</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8257</v>
+        <v>0.0975</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1473</v>
+        <v>0.1743</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LIMA</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0582</v>
+        <v>-0.08</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1218</v>
+        <v>-1.8369</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0636</v>
+        <v>1.7569</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0304</v>
+        <v>-1.4016</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3449</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3145</v>
+        <v>-0.4545</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0173</v>
+        <v>-1.2035</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>-0.6592</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0477</v>
+        <v>-0.1981</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3622</v>
+        <v>-0.2879</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3145</v>
+        <v>0.0898</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0278</v>
+        <v>0.3216</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1391</v>
+        <v>-0.04</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1113</v>
+        <v>0.3616</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2629</v>
+        <v>-0.1504</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1491</v>
+        <v>-0.7396</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8862</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3853</v>
+        <v>-3.1109</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9348</v>
+        <v>-2.4765</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4505</v>
+        <v>-0.6343</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1651</v>
+        <v>-2.0076</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6345</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5306</v>
+        <v>-1.3559</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2203</v>
+        <v>-1.1032</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3003</v>
+        <v>-1.8248</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.7215</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1225</v>
+        <v>0.6026</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3962</v>
+        <v>0.2759</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5187</v>
+        <v>0.3267</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5463</v>
+        <v>3.2684</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>3.2684</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3732</v>
+        <v>-0.1645</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-1.6715</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3732</v>
+        <v>1.507</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3732</v>
+        <v>-2.119</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3732</v>
+        <v>-1.2082</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1.7919</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.1401</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3271</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.259</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3732</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.3611</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.1204</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.2407</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7111</v>
+        <v>-0.3724</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2234</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5123</v>
+        <v>-0.3724</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.2953</v>
+        <v>-0.3724</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.7268</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4315</v>
+        <v>-0.3724</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7555</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.5765</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.821</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.3724</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1503</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6105</v>
+        <v>-0.3724</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.722</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7864</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8419</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9445</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4783</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.128</v>
+        <v>-1.3147</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8902</v>
+        <v>-1.026</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2377</v>
+        <v>-0.2887</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3146</v>
+        <v>-0.3208</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3492</v>
+        <v>-0.3503</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0346</v>
+        <v>0.0296</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3337</v>
+        <v>-0.35</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0192</v>
+        <v>0.0292</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4815</v>
+        <v>0.302</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5777</v>
+        <v>0.4621</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1601</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6462</v>
+        <v>-1.8936</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0122</v>
+        <v>-2.9183</v>
       </c>
       <c r="F23" t="n">
-        <v>0.366</v>
+        <v>1.0247</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1305</v>
+        <v>-4.35</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4908</v>
+        <v>-1.8667</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6397</v>
+        <v>-2.4833</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9966</v>
+        <v>-3.5057</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6478</v>
+        <v>-1.2485</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3488</v>
+        <v>-2.2572</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1338</v>
+        <v>-0.8442</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8429</v>
+        <v>-0.6182</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7091</v>
+        <v>-0.226</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8865</v>
+        <v>0.2287</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0253</v>
+        <v>-0.5021</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1388</v>
+        <v>0.7308</v>
       </c>
       <c r="V23" t="n">
-        <v>3.278</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>3.278</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5518</v>
+        <v>-2.309</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3618</v>
+        <v>-5.922</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.613</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.3459</v>
+        <v>-4.3067</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8643</v>
+        <v>-5.746</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.4816</v>
+        <v>1.4393</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.4806</v>
+        <v>-3.7915</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2335</v>
+        <v>-4.6107</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2471</v>
+        <v>0.8192</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8653</v>
+        <v>-0.5152</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6308</v>
+        <v>-1.1353</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2345</v>
+        <v>0.6201</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>2.7316</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4328</v>
+        <v>1.2041</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9739</v>
+        <v>0.1945</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5411</v>
+        <v>1.0096</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0927</v>
+        <v>1.4764</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.423500000000001</v>
+        <v>-8.7964</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.9328</v>
+        <v>-8.285600000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4907</v>
+        <v>-0.5109</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.5141</v>
+        <v>-5.5292</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.4341</v>
+        <v>-5.4394</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08</v>
+        <v>-0.0898</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2548</v>
+        <v>-4.2969</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.0947</v>
+        <v>-4.1173</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.1601</v>
+        <v>-0.1796</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.2593</v>
+        <v>-1.2323</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O25" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.5538</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.234</v>
+        <v>-0.5255</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1393</v>
+        <v>1.0793</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.7485</v>
+        <v>-10.963</v>
       </c>
       <c r="E26" t="n">
-        <v>-20.1565</v>
+        <v>-20.4795</v>
       </c>
       <c r="F26" t="n">
-        <v>8.4079</v>
+        <v>9.516399999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-20.0811</v>
+        <v>-20.1084</v>
       </c>
       <c r="H26" t="n">
-        <v>-20.3743</v>
+        <v>-20.3908</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2932000000000002</v>
+        <v>0.2826000000000007</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.8967</v>
+        <v>-12.1668</v>
       </c>
       <c r="K26" t="n">
-        <v>-11.3896</v>
+        <v>-11.5512</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5072000000000004</v>
+        <v>-0.6155000000000007</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.1843</v>
+        <v>-7.9415</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.9846</v>
+        <v>-8.839699999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8003000000000001</v>
+        <v>0.8981</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8784</v>
+        <v>-15.9343</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S26" t="n">
-        <v>4.9903</v>
+        <v>5.8053</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.03019999999999978</v>
+        <v>-0.004999999999999893</v>
       </c>
       <c r="U26" t="n">
-        <v>5.0205</v>
+        <v>5.8103</v>
       </c>
       <c r="V26" t="n">
-        <v>3.3422</v>
+        <v>3.339700000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>7.6487</v>
+        <v>7.626300000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.3065</v>
+        <v>-4.2865</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104615_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104615_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.626200000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104615_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.2865</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
